--- a/artfynd/A 20970-2020 artfynd.xlsx
+++ b/artfynd/A 20970-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121518454</v>
+        <v>121518471</v>
       </c>
       <c r="B2" t="n">
-        <v>91118</v>
+        <v>94870</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579405</v>
+        <v>579449</v>
       </c>
       <c r="R2" t="n">
-        <v>6314360</v>
+        <v>6314379</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121518471</v>
+        <v>121518454</v>
       </c>
       <c r="B3" t="n">
-        <v>94870</v>
+        <v>91118</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,31 +802,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579449</v>
+        <v>579405</v>
       </c>
       <c r="R3" t="n">
-        <v>6314379</v>
+        <v>6314360</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 20970-2020 artfynd.xlsx
+++ b/artfynd/A 20970-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121518471</v>
+        <v>121518454</v>
       </c>
       <c r="B2" t="n">
-        <v>94870</v>
+        <v>91124</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579449</v>
+        <v>579405</v>
       </c>
       <c r="R2" t="n">
-        <v>6314379</v>
+        <v>6314360</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121518454</v>
+        <v>121518471</v>
       </c>
       <c r="B3" t="n">
-        <v>91118</v>
+        <v>94876</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,30 +801,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579405</v>
+        <v>579449</v>
       </c>
       <c r="R3" t="n">
-        <v>6314360</v>
+        <v>6314379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 20970-2020 artfynd.xlsx
+++ b/artfynd/A 20970-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121518454</v>
       </c>
       <c r="B2" t="n">
-        <v>91124</v>
+        <v>91125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>121518471</v>
       </c>
       <c r="B3" t="n">
-        <v>94876</v>
+        <v>94877</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 20970-2020 artfynd.xlsx
+++ b/artfynd/A 20970-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121518454</v>
+        <v>121518471</v>
       </c>
       <c r="B2" t="n">
-        <v>91125</v>
+        <v>94877</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579405</v>
+        <v>579449</v>
       </c>
       <c r="R2" t="n">
-        <v>6314360</v>
+        <v>6314379</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121518471</v>
+        <v>121518454</v>
       </c>
       <c r="B3" t="n">
-        <v>94877</v>
+        <v>91125</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,31 +802,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579449</v>
+        <v>579405</v>
       </c>
       <c r="R3" t="n">
-        <v>6314379</v>
+        <v>6314360</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 20970-2020 artfynd.xlsx
+++ b/artfynd/A 20970-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121518471</v>
       </c>
       <c r="B2" t="n">
-        <v>94877</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>121518454</v>
       </c>
       <c r="B3" t="n">
-        <v>91125</v>
+        <v>91133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 20970-2020 artfynd.xlsx
+++ b/artfynd/A 20970-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121518454</v>
+        <v>121518471</v>
       </c>
       <c r="B2" t="n">
-        <v>91133</v>
+        <v>94885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,30 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -722,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579405</v>
+        <v>579449</v>
       </c>
       <c r="R2" t="n">
-        <v>6314360</v>
+        <v>6314379</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121518471</v>
+        <v>121518454</v>
       </c>
       <c r="B3" t="n">
-        <v>94885</v>
+        <v>91133</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,31 +802,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579449</v>
+        <v>579405</v>
       </c>
       <c r="R3" t="n">
-        <v>6314379</v>
+        <v>6314360</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 20970-2020 artfynd.xlsx
+++ b/artfynd/A 20970-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121518471</v>
+        <v>121518454</v>
       </c>
       <c r="B2" t="n">
-        <v>94885</v>
+        <v>91133</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,30 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579449</v>
+        <v>579405</v>
       </c>
       <c r="R2" t="n">
-        <v>6314379</v>
+        <v>6314360</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121518454</v>
+        <v>121518471</v>
       </c>
       <c r="B3" t="n">
-        <v>91133</v>
+        <v>94885</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,30 +801,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579405</v>
+        <v>579449</v>
       </c>
       <c r="R3" t="n">
-        <v>6314360</v>
+        <v>6314379</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 20970-2020 artfynd.xlsx
+++ b/artfynd/A 20970-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -894,6 +894,123 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126632366</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57654</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Merehäll, Merehäll, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>579412</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6314364</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ålem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ser den här ibland.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian  Norrby</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20970-2020 artfynd.xlsx
+++ b/artfynd/A 20970-2020 artfynd.xlsx
@@ -1016,7 +1016,7 @@
         <v>127014332</v>
       </c>
       <c r="B5" t="n">
-        <v>95964</v>
+        <v>96039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
